--- a/research/traditional_assets/database/data/greece/greece_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,40 +588,40 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.29415</v>
+        <v>0.154</v>
       </c>
       <c r="E2">
-        <v>0.376</v>
+        <v>0.636</v>
       </c>
       <c r="F2">
-        <v>0.29</v>
+        <v>0.162</v>
       </c>
       <c r="G2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>-6954.2</v>
+        <v>2798.7</v>
       </c>
       <c r="L2">
-        <v>17.64129883307964</v>
+        <v>0.2937034316297618</v>
       </c>
       <c r="M2">
-        <v>19.7</v>
+        <v>66.7</v>
       </c>
       <c r="N2">
-        <v>0.001677880930074099</v>
+        <v>0.006829538007863696</v>
       </c>
       <c r="O2">
-        <v>-0.002832820453826464</v>
+        <v>0.02383249365776968</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -630,64 +630,64 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>19.7</v>
+        <v>66.7</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>55265.1</v>
+        <v>49917.6</v>
       </c>
       <c r="V2">
-        <v>4.707018141555234</v>
+        <v>5.111156618610747</v>
       </c>
       <c r="W2">
-        <v>-0.2964840903570561</v>
+        <v>0.1264594663814273</v>
       </c>
       <c r="X2">
-        <v>0.2225864249605027</v>
+        <v>0.2773250486779398</v>
       </c>
       <c r="Y2">
-        <v>-0.5190705153175589</v>
+        <v>-0.1508655822965125</v>
       </c>
       <c r="Z2">
-        <v>-0.007073541867041824</v>
+        <v>0.2923149602434475</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08801329429897989</v>
+        <v>0.1507764736631935</v>
       </c>
       <c r="AC2">
-        <v>-0.08801329429897989</v>
+        <v>-0.1507764736631935</v>
       </c>
       <c r="AD2">
-        <v>60247.5</v>
+        <v>50400.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>60247.5</v>
+        <v>50400.1</v>
       </c>
       <c r="AG2">
-        <v>4982.400000000001</v>
+        <v>482.5</v>
       </c>
       <c r="AH2">
-        <v>0.8369045055807525</v>
+        <v>0.8376771126789825</v>
       </c>
       <c r="AI2">
-        <v>0.6864474273389458</v>
+        <v>0.7322700908942976</v>
       </c>
       <c r="AJ2">
-        <v>0.2979298468014878</v>
+        <v>0.04707822302881285</v>
       </c>
       <c r="AK2">
-        <v>0.153295181834964</v>
+        <v>0.02551613995007827</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Attica Bank S.A. (ATSE:TATT)</t>
+          <t>National Bank of Greece S.A. (ATSE:ETE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,32 +712,38 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.114</v>
+      </c>
+      <c r="F3">
+        <v>0.13</v>
+      </c>
       <c r="G3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>-344.9</v>
+        <v>764.9</v>
       </c>
       <c r="L3">
-        <v>1.679162609542356</v>
+        <v>0.4773762716095613</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>14.7</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.004013213573944142</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.01921819845731468</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -746,61 +752,64 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>14.7</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>17230.8</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>4.70414152720522</v>
       </c>
       <c r="W3">
-        <v>-0.6469705496154567</v>
+        <v>0.1159448848736566</v>
       </c>
       <c r="X3">
-        <v>0.05977689079377755</v>
+        <v>0.2564516315964158</v>
       </c>
       <c r="Y3">
-        <v>-0.7067474404092343</v>
+        <v>-0.1405067467227592</v>
       </c>
       <c r="Z3">
-        <v>-0.3296950240770465</v>
+        <v>0.1338048751972876</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05977689079377755</v>
+        <v>0.1319198113548637</v>
       </c>
       <c r="AC3">
-        <v>-0.05977689079377755</v>
+        <v>-0.1319198113548637</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>14325.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>14325.4</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>-2905.4</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.7963731981343429</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.708452229645858</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-3.835511551155113</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>-0.9717381852235858</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,13 +835,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.09329999999999999</v>
+        <v>0.154</v>
       </c>
       <c r="E4">
-        <v>0.376</v>
+        <v>0.636</v>
       </c>
       <c r="F4">
-        <v>0.09050000000000001</v>
+        <v>0.194</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -847,10 +856,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>97.40000000000001</v>
+        <v>1194.4</v>
       </c>
       <c r="L4">
-        <v>0.0562810585923957</v>
+        <v>0.5392811992053459</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -874,55 +883,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>13098.1</v>
+        <v>15141.2</v>
       </c>
       <c r="V4">
-        <v>3.483629883773505</v>
+        <v>3.619093147214189</v>
       </c>
       <c r="W4">
-        <v>0.01550980111148267</v>
+        <v>0.1883971103189375</v>
       </c>
       <c r="X4">
-        <v>0.2225864249605027</v>
+        <v>0.2773250486779398</v>
       </c>
       <c r="Y4">
-        <v>-0.2070766238490201</v>
+        <v>-0.08892793835900231</v>
       </c>
       <c r="Z4">
-        <v>0.103467036547671</v>
+        <v>0.1965182516725524</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07525593890570398</v>
+        <v>0.1507764736631935</v>
       </c>
       <c r="AC4">
-        <v>-0.07525593890570398</v>
+        <v>-0.1507764736631935</v>
       </c>
       <c r="AD4">
-        <v>18028.5</v>
+        <v>18445.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>18028.5</v>
+        <v>18445.8</v>
       </c>
       <c r="AG4">
-        <v>4930.4</v>
+        <v>3304.599999999999</v>
       </c>
       <c r="AH4">
-        <v>0.8274356997301315</v>
+        <v>0.8151218542168408</v>
       </c>
       <c r="AI4">
-        <v>0.7398341287656505</v>
+        <v>0.7453751969935749</v>
       </c>
       <c r="AJ4">
-        <v>0.5673452009711978</v>
+        <v>0.4413017640853063</v>
       </c>
       <c r="AK4">
-        <v>0.4374722720093698</v>
+        <v>0.3440213204522267</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -939,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>National Bank of Greece S.A. (ATSE:ETE)</t>
+          <t>Piraeus Financial Holdings S.A. (ATSE:TPEIR)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -948,10 +957,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.495</v>
-      </c>
-      <c r="F5">
-        <v>0.38</v>
+        <v>0.401</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -966,19 +972,19 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>398.7</v>
+        <v>839.4</v>
       </c>
       <c r="L5">
-        <v>0.2043986465702861</v>
+        <v>0.146956354277911</v>
       </c>
       <c r="M5">
-        <v>19.7</v>
+        <v>52</v>
       </c>
       <c r="N5">
-        <v>0.006459863588667366</v>
+        <v>0.02708615480779248</v>
       </c>
       <c r="O5">
-        <v>0.04941058439929772</v>
+        <v>0.0619490111984751</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -990,295 +996,66 @@
         <v>-0</v>
       </c>
       <c r="S5">
-        <v>19.7</v>
+        <v>52</v>
       </c>
       <c r="T5">
         <v>1</v>
       </c>
       <c r="U5">
-        <v>13287</v>
+        <v>17545.6</v>
       </c>
       <c r="V5">
-        <v>4.356964847848898</v>
+        <v>9.139285342223149</v>
       </c>
       <c r="W5">
-        <v>0.06257553166444323</v>
+        <v>0.1264594663814273</v>
       </c>
       <c r="X5">
-        <v>0.267591940563797</v>
+        <v>0.47740321463567</v>
       </c>
       <c r="Y5">
-        <v>-0.2050164088993538</v>
+        <v>-0.3509437482542427</v>
       </c>
       <c r="Z5">
-        <v>0.1147594029640002</v>
+        <v>0.6106828605946564</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.08801329429897989</v>
+        <v>0.156969409624495</v>
       </c>
       <c r="AC5">
-        <v>-0.08801329429897989</v>
+        <v>-0.156969409624495</v>
       </c>
       <c r="AD5">
-        <v>18664.8</v>
+        <v>17628.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>18664.8</v>
+        <v>17628.9</v>
       </c>
       <c r="AG5">
-        <v>5377.799999999999</v>
+        <v>83.30000000000291</v>
       </c>
       <c r="AH5">
-        <v>0.8595586339019269</v>
+        <v>0.9017939811854497</v>
       </c>
       <c r="AI5">
-        <v>0.7381388340722052</v>
+        <v>0.7388629267168214</v>
       </c>
       <c r="AJ5">
-        <v>0.638132757434084</v>
+        <v>0.04158554240926703</v>
       </c>
       <c r="AK5">
-        <v>0.4481761436083771</v>
+        <v>0.01319311360648773</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Greece</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Alpha Services and Holdings S.A. (ATSE:ALPHA)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="F6">
-        <v>0.29</v>
-      </c>
-      <c r="G6">
-        <v>-0</v>
-      </c>
-      <c r="H6">
-        <v>-0</v>
-      </c>
-      <c r="I6">
-        <v>-0</v>
-      </c>
-      <c r="J6">
-        <v>-0</v>
-      </c>
-      <c r="K6">
-        <v>-2929.5</v>
-      </c>
-      <c r="L6">
-        <v>2.023554603854389</v>
-      </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>13470.9</v>
-      </c>
-      <c r="V6">
-        <v>4.688139486322823</v>
-      </c>
-      <c r="W6">
-        <v>-0.2964840903570561</v>
-      </c>
-      <c r="X6">
-        <v>0.1239362893144358</v>
-      </c>
-      <c r="Y6">
-        <v>-0.420420379671492</v>
-      </c>
-      <c r="Z6">
-        <v>-0.1647060162009648</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.08855770173016668</v>
-      </c>
-      <c r="AC6">
-        <v>-0.08855770173016668</v>
-      </c>
-      <c r="AD6">
-        <v>5429.5</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>5429.5</v>
-      </c>
-      <c r="AG6">
-        <v>-8041.4</v>
-      </c>
-      <c r="AH6">
-        <v>0.6539281455876863</v>
-      </c>
-      <c r="AI6">
-        <v>0.4172077547852681</v>
-      </c>
-      <c r="AJ6">
-        <v>1.555998452012384</v>
-      </c>
-      <c r="AK6">
-        <v>17.59606126914661</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Greece</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Piraeus Financial Holdings S.A. (ATSE:TPEIR)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="G7">
-        <v>-0</v>
-      </c>
-      <c r="H7">
-        <v>-0</v>
-      </c>
-      <c r="I7">
-        <v>-0</v>
-      </c>
-      <c r="J7">
-        <v>-0</v>
-      </c>
-      <c r="K7">
-        <v>-4175.9</v>
-      </c>
-      <c r="L7">
-        <v>1.723940056970648</v>
-      </c>
-      <c r="M7">
-        <v>-0</v>
-      </c>
-      <c r="N7">
-        <v>-0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>15409.1</v>
-      </c>
-      <c r="V7">
-        <v>8.400992258205212</v>
-      </c>
-      <c r="W7">
-        <v>-0.4717678159880699</v>
-      </c>
-      <c r="X7">
-        <v>0.3952986356161442</v>
-      </c>
-      <c r="Y7">
-        <v>-0.8670664516042141</v>
-      </c>
-      <c r="Z7">
-        <v>-0.1923559494314211</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.09974441264459982</v>
-      </c>
-      <c r="AC7">
-        <v>-0.09974441264459982</v>
-      </c>
-      <c r="AD7">
-        <v>18124.7</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>18124.7</v>
-      </c>
-      <c r="AG7">
-        <v>2715.6</v>
-      </c>
-      <c r="AH7">
-        <v>0.9081011478588499</v>
-      </c>
-      <c r="AI7">
-        <v>0.7282300803175739</v>
-      </c>
-      <c r="AJ7">
-        <v>0.596861400501121</v>
-      </c>
-      <c r="AK7">
-        <v>0.2864677834507786</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/greece/greece_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.154</v>
+        <v>0.224</v>
       </c>
       <c r="E2">
-        <v>0.636</v>
+        <v>0.5760000000000001</v>
       </c>
       <c r="F2">
-        <v>0.162</v>
+        <v>-0.002125</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,19 +609,19 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>2798.7</v>
+        <v>3016.4</v>
       </c>
       <c r="L2">
-        <v>0.2937034316297618</v>
+        <v>0.4059102163849714</v>
       </c>
       <c r="M2">
-        <v>66.7</v>
+        <v>147.1</v>
       </c>
       <c r="N2">
-        <v>0.006829538007863696</v>
+        <v>0.008167911380104944</v>
       </c>
       <c r="O2">
-        <v>0.02383249365776968</v>
+        <v>0.04876674181143084</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -633,61 +633,61 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>66.7</v>
+        <v>147.1</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>49917.6</v>
+        <v>34729.5</v>
       </c>
       <c r="V2">
-        <v>5.111156618610747</v>
+        <v>1.928398900580249</v>
       </c>
       <c r="W2">
-        <v>0.1264594663814273</v>
+        <v>0.1661714225651238</v>
       </c>
       <c r="X2">
-        <v>0.2773250486779398</v>
+        <v>0.1095203860434481</v>
       </c>
       <c r="Y2">
-        <v>-0.1508655822965125</v>
+        <v>0.05665103652167569</v>
       </c>
       <c r="Z2">
-        <v>0.2923149602434475</v>
+        <v>0.3912702382519415</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1507764736631935</v>
+        <v>0.08706971947111064</v>
       </c>
       <c r="AC2">
-        <v>-0.1507764736631935</v>
+        <v>-0.08706971947111064</v>
       </c>
       <c r="AD2">
-        <v>50400.1</v>
+        <v>31956.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>50400.1</v>
+        <v>31956.1</v>
       </c>
       <c r="AG2">
-        <v>482.5</v>
+        <v>-2773.400000000001</v>
       </c>
       <c r="AH2">
-        <v>0.8376771126789825</v>
+        <v>0.6395620186688441</v>
       </c>
       <c r="AI2">
-        <v>0.7322700908942976</v>
+        <v>0.5729538515050838</v>
       </c>
       <c r="AJ2">
-        <v>0.04707822302881285</v>
+        <v>-0.1820282093186578</v>
       </c>
       <c r="AK2">
-        <v>0.02551613995007827</v>
+        <v>-0.1317855242150081</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>National Bank of Greece S.A. (ATSE:ETE)</t>
+          <t>Attica Bank S.A. (ATSE:TATT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,38 +712,17 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.114</v>
-      </c>
-      <c r="F3">
-        <v>0.13</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
       <c r="K3">
-        <v>764.9</v>
-      </c>
-      <c r="L3">
-        <v>0.4773762716095613</v>
+        <v>-349.3</v>
       </c>
       <c r="M3">
-        <v>14.7</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.004013213573944142</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.01921819845731468</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,64 +731,61 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>14.7</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>17230.8</v>
+        <v>422.7</v>
       </c>
       <c r="V3">
-        <v>4.70414152720522</v>
+        <v>0.6695707270711231</v>
       </c>
       <c r="W3">
-        <v>0.1159448848736566</v>
+        <v>-1.228199718706048</v>
       </c>
       <c r="X3">
-        <v>0.2564516315964158</v>
+        <v>0.07604479732822418</v>
       </c>
       <c r="Y3">
-        <v>-0.1405067467227592</v>
+        <v>-1.304244516034272</v>
       </c>
       <c r="Z3">
-        <v>0.1338048751972876</v>
+        <v>0</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1319198113548637</v>
+        <v>0.07490070033844062</v>
       </c>
       <c r="AC3">
-        <v>-0.1319198113548637</v>
+        <v>-0.07490070033844062</v>
       </c>
       <c r="AD3">
-        <v>14325.4</v>
+        <v>117.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>14325.4</v>
+        <v>117.6</v>
       </c>
       <c r="AG3">
-        <v>-2905.4</v>
+        <v>-305.1</v>
       </c>
       <c r="AH3">
-        <v>0.7963731981343429</v>
+        <v>0.1570303111229804</v>
       </c>
       <c r="AI3">
-        <v>0.708452229645858</v>
+        <v>0.2062796000701631</v>
       </c>
       <c r="AJ3">
-        <v>-3.835511551155113</v>
+        <v>-0.9353157572041695</v>
       </c>
       <c r="AK3">
-        <v>-0.9717381852235858</v>
+        <v>-2.06987788331072</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,7 +802,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eurobank Ergasias Services and Holdings S.A. (ATSE:EUROB)</t>
+          <t>National Bank of Greece S.A. (ATSE:ETE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,13 +811,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.154</v>
-      </c>
-      <c r="E4">
-        <v>0.636</v>
-      </c>
-      <c r="F4">
-        <v>0.194</v>
+        <v>0.224</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,19 +826,19 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1194.4</v>
+        <v>1302.9</v>
       </c>
       <c r="L4">
-        <v>0.5392811992053459</v>
+        <v>0.4881054958228749</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>10.6</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.001667033623753656</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.008135697290659298</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -880,58 +850,61 @@
         <v>-0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>10.6</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>15141.2</v>
+        <v>8890.799999999999</v>
       </c>
       <c r="V4">
-        <v>3.619093147214189</v>
+        <v>1.398232315289529</v>
       </c>
       <c r="W4">
-        <v>0.1883971103189375</v>
+        <v>0.2218570674476817</v>
       </c>
       <c r="X4">
-        <v>0.2773250486779398</v>
+        <v>0.09678396445016209</v>
       </c>
       <c r="Y4">
-        <v>-0.08892793835900231</v>
+        <v>0.1250731029975196</v>
       </c>
       <c r="Z4">
-        <v>0.1965182516725524</v>
+        <v>0.8995720014828298</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1507764736631935</v>
+        <v>0.08274419041960604</v>
       </c>
       <c r="AC4">
-        <v>-0.1507764736631935</v>
+        <v>-0.08274419041960604</v>
       </c>
       <c r="AD4">
-        <v>18445.8</v>
+        <v>6383.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>18445.8</v>
+        <v>6383.4</v>
       </c>
       <c r="AG4">
-        <v>3304.599999999999</v>
+        <v>-2507.4</v>
       </c>
       <c r="AH4">
-        <v>0.8151218542168408</v>
+        <v>0.5009731596295715</v>
       </c>
       <c r="AI4">
-        <v>0.7453751969935749</v>
+        <v>0.4528133246318418</v>
       </c>
       <c r="AJ4">
-        <v>0.4413017640853063</v>
+        <v>-0.6510697964270874</v>
       </c>
       <c r="AK4">
-        <v>0.3440213204522267</v>
+        <v>-0.4815995697602949</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,114 +921,239 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Eurobank Ergasias Services and Holdings S.A. (ATSE:EUROB)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.139</v>
+      </c>
+      <c r="E5">
+        <v>0.5760000000000001</v>
+      </c>
+      <c r="F5">
+        <v>-0.00749</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>1274.3</v>
+      </c>
+      <c r="L5">
+        <v>0.5266572987270624</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>12260.8</v>
+      </c>
+      <c r="V5">
+        <v>1.85460595976403</v>
+      </c>
+      <c r="W5">
+        <v>0.2052310318725741</v>
+      </c>
+      <c r="X5">
+        <v>0.1222568076367341</v>
+      </c>
+      <c r="Y5">
+        <v>0.08297422423583997</v>
+      </c>
+      <c r="Z5">
+        <v>0.2543279691392413</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.09139524852261524</v>
+      </c>
+      <c r="AC5">
+        <v>-0.09139524852261524</v>
+      </c>
+      <c r="AD5">
+        <v>13275.8</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>13275.8</v>
+      </c>
+      <c r="AG5">
+        <v>1015</v>
+      </c>
+      <c r="AH5">
+        <v>0.6675684373554317</v>
+      </c>
+      <c r="AI5">
+        <v>0.6213720378370535</v>
+      </c>
+      <c r="AJ5">
+        <v>0.1330972987149226</v>
+      </c>
+      <c r="AK5">
+        <v>0.111483332418035</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Piraeus Financial Holdings S.A. (ATSE:TPEIR)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.401</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>839.4</v>
-      </c>
-      <c r="L5">
-        <v>0.146956354277911</v>
-      </c>
-      <c r="M5">
-        <v>52</v>
-      </c>
-      <c r="N5">
-        <v>0.02708615480779248</v>
-      </c>
-      <c r="O5">
-        <v>0.0619490111984751</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>-0</v>
-      </c>
-      <c r="S5">
-        <v>52</v>
-      </c>
-      <c r="T5">
+      <c r="D6">
+        <v>0.754</v>
+      </c>
+      <c r="F6">
+        <v>0.00324</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>788.5</v>
+      </c>
+      <c r="L6">
+        <v>0.3366349314776075</v>
+      </c>
+      <c r="M6">
+        <v>136.5</v>
+      </c>
+      <c r="N6">
+        <v>0.0309622102254684</v>
+      </c>
+      <c r="O6">
+        <v>0.1731135066582118</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>-0</v>
+      </c>
+      <c r="S6">
+        <v>136.5</v>
+      </c>
+      <c r="T6">
         <v>1</v>
       </c>
-      <c r="U5">
-        <v>17545.6</v>
-      </c>
-      <c r="V5">
-        <v>9.139285342223149</v>
-      </c>
-      <c r="W5">
-        <v>0.1264594663814273</v>
-      </c>
-      <c r="X5">
-        <v>0.47740321463567</v>
-      </c>
-      <c r="Y5">
-        <v>-0.3509437482542427</v>
-      </c>
-      <c r="Z5">
-        <v>0.6106828605946564</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.156969409624495</v>
-      </c>
-      <c r="AC5">
-        <v>-0.156969409624495</v>
-      </c>
-      <c r="AD5">
-        <v>17628.9</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>17628.9</v>
-      </c>
-      <c r="AG5">
-        <v>83.30000000000291</v>
-      </c>
-      <c r="AH5">
-        <v>0.9017939811854497</v>
-      </c>
-      <c r="AI5">
-        <v>0.7388629267168214</v>
-      </c>
-      <c r="AJ5">
-        <v>0.04158554240926703</v>
-      </c>
-      <c r="AK5">
-        <v>0.01319311360648773</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
+      <c r="U6">
+        <v>13155.2</v>
+      </c>
+      <c r="V6">
+        <v>2.983985845846754</v>
+      </c>
+      <c r="W6">
+        <v>0.1271118132576735</v>
+      </c>
+      <c r="X6">
+        <v>0.1413945877557155</v>
+      </c>
+      <c r="Y6">
+        <v>-0.01428277449804205</v>
+      </c>
+      <c r="Z6">
+        <v>0.3725920623558417</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.0960680776177654</v>
+      </c>
+      <c r="AC6">
+        <v>-0.0960680776177654</v>
+      </c>
+      <c r="AD6">
+        <v>12179.3</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>12179.3</v>
+      </c>
+      <c r="AG6">
+        <v>-975.9000000000015</v>
+      </c>
+      <c r="AH6">
+        <v>0.7342279613453179</v>
+      </c>
+      <c r="AI6">
+        <v>0.6169326856349757</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.2842951612433366</v>
+      </c>
+      <c r="AK6">
+        <v>-0.1481667046230929</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/greece/greece_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.224</v>
+        <v>0.1745</v>
       </c>
       <c r="E2">
-        <v>0.5760000000000001</v>
+        <v>0.4205</v>
       </c>
       <c r="F2">
-        <v>-0.002125</v>
+        <v>0.0291</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3016.4</v>
+        <v>4787.6</v>
       </c>
       <c r="L2">
-        <v>0.4059102163849714</v>
+        <v>0.4244100491108629</v>
       </c>
       <c r="M2">
-        <v>147.1</v>
+        <v>1231.362</v>
       </c>
       <c r="N2">
-        <v>0.008167911380104944</v>
+        <v>0.05011995131938311</v>
       </c>
       <c r="O2">
-        <v>0.04876674181143084</v>
+        <v>0.2571981786281227</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>907.862</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.03695257710138675</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.1896277884535049</v>
       </c>
       <c r="S2">
-        <v>147.1</v>
+        <v>323.5</v>
       </c>
       <c r="T2">
-        <v>1</v>
+        <v>0.2627172188194861</v>
       </c>
       <c r="U2">
-        <v>34729.5</v>
+        <v>45115.6</v>
       </c>
       <c r="V2">
-        <v>1.928398900580249</v>
+        <v>1.836333812270283</v>
       </c>
       <c r="W2">
-        <v>0.1661714225651238</v>
+        <v>0.1714870402078184</v>
       </c>
       <c r="X2">
-        <v>0.1095203860434481</v>
+        <v>0.1183919781539885</v>
       </c>
       <c r="Y2">
-        <v>0.05665103652167569</v>
+        <v>0.05309506205382991</v>
       </c>
       <c r="Z2">
-        <v>0.3912702382519415</v>
+        <v>0.2930452221621846</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08706971947111064</v>
+        <v>0.08918118042436471</v>
       </c>
       <c r="AC2">
-        <v>-0.08706971947111064</v>
+        <v>-0.08918118042436471</v>
       </c>
       <c r="AD2">
-        <v>31956.1</v>
+        <v>37606.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>31956.1</v>
+        <v>37606.9</v>
       </c>
       <c r="AG2">
-        <v>-2773.400000000001</v>
+        <v>-7508.699999999997</v>
       </c>
       <c r="AH2">
-        <v>0.6395620186688441</v>
+        <v>0.6048537037275313</v>
       </c>
       <c r="AI2">
-        <v>0.5729538515050838</v>
+        <v>0.4986210883325511</v>
       </c>
       <c r="AJ2">
-        <v>-0.1820282093186578</v>
+        <v>-0.4401451382212945</v>
       </c>
       <c r="AK2">
-        <v>-0.1317855242150081</v>
+        <v>-0.2477611841801346</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Attica Bank S.A. (ATSE:TATT)</t>
+          <t>National Bank of Greece S.A. (ATSE:ETE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,80 +712,107 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.168</v>
+      </c>
+      <c r="E3">
+        <v>0.381</v>
+      </c>
+      <c r="F3">
+        <v>-0.0274</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
       <c r="K3">
-        <v>-349.3</v>
+        <v>1449.9</v>
+      </c>
+      <c r="L3">
+        <v>0.4644435902364021</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>416</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.05755634572547284</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.2869163390578661</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>370.3</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.05123344909168892</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.255396923925788</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>45.69999999999999</v>
+      </c>
+      <c r="T3">
+        <v>0.1098557692307692</v>
       </c>
       <c r="U3">
-        <v>422.7</v>
+        <v>9366.5</v>
       </c>
       <c r="V3">
-        <v>0.6695707270711231</v>
+        <v>1.295917096725099</v>
       </c>
       <c r="W3">
-        <v>-1.228199718706048</v>
+        <v>0.1886097849700155</v>
       </c>
       <c r="X3">
-        <v>0.07604479732822418</v>
+        <v>0.09281167056832641</v>
       </c>
       <c r="Y3">
-        <v>-1.304244516034272</v>
+        <v>0.09579811440168907</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>0.6026757273306433</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07490070033844062</v>
+        <v>0.08212996339228019</v>
       </c>
       <c r="AC3">
-        <v>-0.07490070033844062</v>
+        <v>-0.08212996339228019</v>
       </c>
       <c r="AD3">
-        <v>117.6</v>
+        <v>5155</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>117.6</v>
+        <v>5155</v>
       </c>
       <c r="AG3">
-        <v>-305.1</v>
+        <v>-4211.5</v>
       </c>
       <c r="AH3">
-        <v>0.1570303111229804</v>
+        <v>0.4163066213346039</v>
       </c>
       <c r="AI3">
-        <v>0.2062796000701631</v>
+        <v>0.3574078054259427</v>
       </c>
       <c r="AJ3">
-        <v>-0.9353157572041695</v>
+        <v>-1.396293349247397</v>
       </c>
       <c r="AK3">
-        <v>-2.06987788331072</v>
+        <v>-0.8328389495333018</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -802,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>National Bank of Greece S.A. (ATSE:ETE)</t>
+          <t>Eurobank Ergasias Services and Holdings S.A. (ATSE:EUROB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -811,7 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.224</v>
+        <v>0.195</v>
+      </c>
+      <c r="E4">
+        <v>0.65</v>
+      </c>
+      <c r="F4">
+        <v>0.0218</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -826,85 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1302.9</v>
+        <v>1444.3</v>
       </c>
       <c r="L4">
-        <v>0.4881054958228749</v>
+        <v>0.456133148054573</v>
       </c>
       <c r="M4">
-        <v>10.6</v>
+        <v>491.8</v>
       </c>
       <c r="N4">
-        <v>0.001667033623753656</v>
+        <v>0.05797272287906829</v>
       </c>
       <c r="O4">
-        <v>0.008135697290659298</v>
+        <v>0.3405109741743405</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>381.4</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.04495891928848444</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.2640725611022641</v>
       </c>
       <c r="S4">
-        <v>10.6</v>
+        <v>110.4</v>
       </c>
       <c r="T4">
-        <v>1</v>
+        <v>0.2244814965433103</v>
       </c>
       <c r="U4">
-        <v>8890.799999999999</v>
+        <v>19417.8</v>
       </c>
       <c r="V4">
-        <v>1.398232315289529</v>
+        <v>2.288944160880789</v>
       </c>
       <c r="W4">
-        <v>0.2218570674476817</v>
+        <v>0.1805239607029473</v>
       </c>
       <c r="X4">
-        <v>0.09678396445016209</v>
+        <v>0.1179653129332525</v>
       </c>
       <c r="Y4">
-        <v>0.1250731029975196</v>
+        <v>0.0625586477696948</v>
       </c>
       <c r="Z4">
-        <v>0.8995720014828298</v>
+        <v>0.1647639167854801</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.08274419041960604</v>
+        <v>0.08877246677849986</v>
       </c>
       <c r="AC4">
-        <v>-0.08274419041960604</v>
+        <v>-0.08877246677849986</v>
       </c>
       <c r="AD4">
-        <v>6383.4</v>
+        <v>15107.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>6383.4</v>
+        <v>15107.1</v>
       </c>
       <c r="AG4">
-        <v>-2507.4</v>
+        <v>-4310.699999999999</v>
       </c>
       <c r="AH4">
-        <v>0.5009731596295715</v>
+        <v>0.6403918543136191</v>
       </c>
       <c r="AI4">
-        <v>0.4528133246318418</v>
+        <v>0.5887595872045894</v>
       </c>
       <c r="AJ4">
-        <v>-0.6510697964270874</v>
+        <v>-1.033096870057038</v>
       </c>
       <c r="AK4">
-        <v>-0.4815995697602949</v>
+        <v>-0.6906623513955199</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -921,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eurobank Ergasias Services and Holdings S.A. (ATSE:EUROB)</t>
+          <t>Alpha Services and Holdings S.A. (ATSE:ALPHA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -930,13 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.139</v>
+        <v>0.157</v>
       </c>
       <c r="E5">
-        <v>0.5760000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="F5">
-        <v>-0.00749</v>
+        <v>0.0364</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -951,82 +984,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>1274.3</v>
+        <v>672.1</v>
       </c>
       <c r="L5">
-        <v>0.5266572987270624</v>
+        <v>0.3441196047309406</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>110.3</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.02836642320748894</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.1641124832614194</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.01771937043514042</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.1025145067698259</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>41.40000000000001</v>
+      </c>
+      <c r="T5">
+        <v>0.3753399818676337</v>
       </c>
       <c r="U5">
-        <v>12260.8</v>
+        <v>4953.9</v>
       </c>
       <c r="V5">
-        <v>1.85460595976403</v>
+        <v>1.274020162534719</v>
       </c>
       <c r="W5">
-        <v>0.2052310318725741</v>
+        <v>0.08895153392096138</v>
       </c>
       <c r="X5">
-        <v>0.1222568076367341</v>
+        <v>0.1263983231757652</v>
       </c>
       <c r="Y5">
-        <v>0.08297422423583997</v>
+        <v>-0.03744678925480378</v>
       </c>
       <c r="Z5">
-        <v>0.2543279691392413</v>
+        <v>0.2585312260079951</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.09139524852261524</v>
+        <v>0.08958989407022958</v>
       </c>
       <c r="AC5">
-        <v>-0.09139524852261524</v>
+        <v>-0.08958989407022958</v>
       </c>
       <c r="AD5">
-        <v>13275.8</v>
+        <v>8316.200000000001</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>13275.8</v>
+        <v>8316.200000000001</v>
       </c>
       <c r="AG5">
-        <v>1015</v>
+        <v>3362.300000000001</v>
       </c>
       <c r="AH5">
-        <v>0.6675684373554317</v>
+        <v>0.6813988168395524</v>
       </c>
       <c r="AI5">
-        <v>0.6213720378370535</v>
+        <v>0.4829160085478026</v>
       </c>
       <c r="AJ5">
-        <v>0.1330972987149226</v>
+        <v>0.463720744204008</v>
       </c>
       <c r="AK5">
-        <v>0.111483332418035</v>
+        <v>0.2740953297084023</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1052,10 +1088,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.754</v>
+        <v>0.181</v>
+      </c>
+      <c r="E6">
+        <v>0.367</v>
       </c>
       <c r="F6">
-        <v>0.00324</v>
+        <v>0.0369</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1070,85 +1109,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>788.5</v>
+        <v>1221.3</v>
       </c>
       <c r="L6">
-        <v>0.3366349314776075</v>
+        <v>0.4018359490672194</v>
       </c>
       <c r="M6">
-        <v>136.5</v>
+        <v>213.262</v>
       </c>
       <c r="N6">
-        <v>0.0309622102254684</v>
+        <v>0.04291935840930589</v>
       </c>
       <c r="O6">
-        <v>0.1731135066582118</v>
+        <v>0.1746188487677066</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>87.262</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.01756163335949607</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.07145009416195858</v>
       </c>
       <c r="S6">
-        <v>136.5</v>
+        <v>126</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>0.5908225562922602</v>
       </c>
       <c r="U6">
-        <v>13155.2</v>
+        <v>11377.4</v>
       </c>
       <c r="V6">
-        <v>2.983985845846754</v>
+        <v>2.289722071283383</v>
       </c>
       <c r="W6">
-        <v>0.1271118132576735</v>
+        <v>0.1624501197126896</v>
       </c>
       <c r="X6">
-        <v>0.1413945877557155</v>
+        <v>0.1188186433747245</v>
       </c>
       <c r="Y6">
-        <v>-0.01428277449804205</v>
+        <v>0.04363147633796502</v>
       </c>
       <c r="Z6">
-        <v>0.3725920623558417</v>
+        <v>0.4645755949924337</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.0960680776177654</v>
+        <v>0.09082676373974205</v>
       </c>
       <c r="AC6">
-        <v>-0.0960680776177654</v>
+        <v>-0.09082676373974205</v>
       </c>
       <c r="AD6">
-        <v>12179.3</v>
+        <v>9028.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>12179.3</v>
+        <v>9028.6</v>
       </c>
       <c r="AG6">
-        <v>-975.9000000000015</v>
+        <v>-2348.799999999999</v>
       </c>
       <c r="AH6">
-        <v>0.7342279613453179</v>
+        <v>0.6450151812823719</v>
       </c>
       <c r="AI6">
-        <v>0.6169326856349757</v>
+        <v>0.498308358859729</v>
       </c>
       <c r="AJ6">
-        <v>-0.2842951612433366</v>
+        <v>-0.8964543338040529</v>
       </c>
       <c r="AK6">
-        <v>-0.1481667046230929</v>
+        <v>-0.3484297814896677</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/research/traditional_assets/database/data/greece/greece_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>4787.6</v>
+        <v>4573.7</v>
       </c>
       <c r="L2">
-        <v>0.4244100491108629</v>
+        <v>0.3962795452970125</v>
       </c>
       <c r="M2">
-        <v>1231.362</v>
+        <v>1269.902</v>
       </c>
       <c r="N2">
-        <v>0.05011995131938311</v>
+        <v>0.04753979425285636</v>
       </c>
       <c r="O2">
-        <v>0.2571981786281227</v>
+        <v>0.2776531036141417</v>
       </c>
       <c r="P2">
-        <v>907.862</v>
+        <v>944.062</v>
       </c>
       <c r="Q2">
-        <v>0.03695257710138675</v>
+        <v>0.03534171396055764</v>
       </c>
       <c r="R2">
-        <v>0.1896277884535049</v>
+        <v>0.2064110020333647</v>
       </c>
       <c r="S2">
-        <v>323.5</v>
+        <v>325.84</v>
       </c>
       <c r="T2">
-        <v>0.2627172188194861</v>
+        <v>0.256586728739698</v>
       </c>
       <c r="U2">
-        <v>45115.6</v>
+        <v>45450.9</v>
       </c>
       <c r="V2">
-        <v>1.836333812270283</v>
+        <v>1.701490693460715</v>
       </c>
       <c r="W2">
         <v>0.1714870402078184</v>
       </c>
       <c r="X2">
-        <v>0.1183919781539885</v>
+        <v>0.1053794622892301</v>
       </c>
       <c r="Y2">
-        <v>0.05309506205382991</v>
+        <v>0.06610757791858834</v>
       </c>
       <c r="Z2">
-        <v>0.2930452221621846</v>
+        <v>0.2950110677715693</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08918118042436471</v>
+        <v>0.08917726867324698</v>
       </c>
       <c r="AC2">
-        <v>-0.08918118042436471</v>
+        <v>-0.08917726867324698</v>
       </c>
       <c r="AD2">
-        <v>37606.9</v>
+        <v>38054.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>37606.9</v>
+        <v>38054.2</v>
       </c>
       <c r="AG2">
-        <v>-7508.699999999997</v>
+        <v>-7396.699999999997</v>
       </c>
       <c r="AH2">
-        <v>0.6048537037275313</v>
+        <v>0.5875590196181365</v>
       </c>
       <c r="AI2">
-        <v>0.4986210883325511</v>
+        <v>0.4964269034989994</v>
       </c>
       <c r="AJ2">
-        <v>-0.4401451382212945</v>
+        <v>-0.3829371961668486</v>
       </c>
       <c r="AK2">
-        <v>-0.2477611841801346</v>
+        <v>-0.2370334526506714</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>National Bank of Greece S.A. (ATSE:ETE)</t>
+          <t>Optima bank S.A. (ATSE:OPTIMA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,15 +712,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.168</v>
-      </c>
-      <c r="E3">
-        <v>0.381</v>
-      </c>
-      <c r="F3">
-        <v>-0.0274</v>
-      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -734,85 +725,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1449.9</v>
+        <v>155.1</v>
       </c>
       <c r="L3">
-        <v>0.4644435902364021</v>
+        <v>0.5942528735632183</v>
       </c>
       <c r="M3">
-        <v>416</v>
+        <v>38.54000000000001</v>
       </c>
       <c r="N3">
-        <v>0.05755634572547284</v>
+        <v>0.03899625619751088</v>
       </c>
       <c r="O3">
-        <v>0.2869163390578661</v>
+        <v>0.2484848484848485</v>
       </c>
       <c r="P3">
-        <v>370.3</v>
+        <v>36.2</v>
       </c>
       <c r="Q3">
-        <v>0.05123344909168892</v>
+        <v>0.0366285540827684</v>
       </c>
       <c r="R3">
-        <v>0.255396923925788</v>
+        <v>0.233397807865893</v>
       </c>
       <c r="S3">
-        <v>45.69999999999999</v>
+        <v>2.340000000000003</v>
       </c>
       <c r="T3">
-        <v>0.1098557692307692</v>
+        <v>0.06071613907628446</v>
       </c>
       <c r="U3">
-        <v>9366.5</v>
+        <v>15.8</v>
       </c>
       <c r="V3">
-        <v>1.295917096725099</v>
+        <v>0.01598704846706466</v>
       </c>
       <c r="W3">
-        <v>0.1886097849700155</v>
+        <v>0.4462025316455696</v>
       </c>
       <c r="X3">
-        <v>0.09281167056832641</v>
+        <v>0.07848381144031245</v>
       </c>
       <c r="Y3">
-        <v>0.09579811440168907</v>
+        <v>0.3677187202052571</v>
       </c>
       <c r="Z3">
-        <v>0.6026757273306433</v>
+        <v>0.5428452579034941</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.08212996339228019</v>
+        <v>0.07669794853065615</v>
       </c>
       <c r="AC3">
-        <v>-0.08212996339228019</v>
+        <v>-0.07669794853065615</v>
       </c>
       <c r="AD3">
-        <v>5155</v>
+        <v>104.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5155</v>
+        <v>104.1</v>
       </c>
       <c r="AG3">
-        <v>-4211.5</v>
+        <v>88.3</v>
       </c>
       <c r="AH3">
-        <v>0.4163066213346039</v>
+        <v>0.09529476382277555</v>
       </c>
       <c r="AI3">
-        <v>0.3574078054259427</v>
+        <v>0.1369736842105263</v>
       </c>
       <c r="AJ3">
-        <v>-1.396293349247397</v>
+        <v>0.08201746238157162</v>
       </c>
       <c r="AK3">
-        <v>-0.8328389495333018</v>
+        <v>0.1186509002956195</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +820,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eurobank Ergasias Services and Holdings S.A. (ATSE:EUROB)</t>
+          <t>National Bank of Greece S.A. (ATSE:ETE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +829,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.195</v>
+        <v>0.168</v>
       </c>
       <c r="E4">
-        <v>0.65</v>
+        <v>0.381</v>
       </c>
       <c r="F4">
-        <v>0.0218</v>
+        <v>-0.0274</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +850,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1444.3</v>
+        <v>1449.9</v>
       </c>
       <c r="L4">
-        <v>0.456133148054573</v>
+        <v>0.4644435902364021</v>
       </c>
       <c r="M4">
-        <v>491.8</v>
+        <v>416</v>
       </c>
       <c r="N4">
-        <v>0.05797272287906829</v>
+        <v>0.05755634572547284</v>
       </c>
       <c r="O4">
-        <v>0.3405109741743405</v>
+        <v>0.2869163390578661</v>
       </c>
       <c r="P4">
-        <v>381.4</v>
+        <v>370.3</v>
       </c>
       <c r="Q4">
-        <v>0.04495891928848444</v>
+        <v>0.05123344909168892</v>
       </c>
       <c r="R4">
-        <v>0.2640725611022641</v>
+        <v>0.255396923925788</v>
       </c>
       <c r="S4">
-        <v>110.4</v>
+        <v>45.69999999999999</v>
       </c>
       <c r="T4">
-        <v>0.2244814965433103</v>
+        <v>0.1098557692307692</v>
       </c>
       <c r="U4">
-        <v>19417.8</v>
+        <v>9366.5</v>
       </c>
       <c r="V4">
-        <v>2.288944160880789</v>
+        <v>1.295917096725099</v>
       </c>
       <c r="W4">
-        <v>0.1805239607029473</v>
+        <v>0.1886097849700155</v>
       </c>
       <c r="X4">
-        <v>0.1179653129332525</v>
+        <v>0.09280454687615419</v>
       </c>
       <c r="Y4">
-        <v>0.0625586477696948</v>
+        <v>0.09580523809386129</v>
       </c>
       <c r="Z4">
-        <v>0.1647639167854801</v>
+        <v>0.6026757273306433</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.08877246677849986</v>
+        <v>0.08212580534032762</v>
       </c>
       <c r="AC4">
-        <v>-0.08877246677849986</v>
+        <v>-0.08212580534032762</v>
       </c>
       <c r="AD4">
-        <v>15107.1</v>
+        <v>5155</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>15107.1</v>
+        <v>5155</v>
       </c>
       <c r="AG4">
-        <v>-4310.699999999999</v>
+        <v>-4211.5</v>
       </c>
       <c r="AH4">
-        <v>0.6403918543136191</v>
+        <v>0.4163066213346039</v>
       </c>
       <c r="AI4">
-        <v>0.5887595872045894</v>
+        <v>0.3574078054259427</v>
       </c>
       <c r="AJ4">
-        <v>-1.033096870057038</v>
+        <v>-1.396293349247397</v>
       </c>
       <c r="AK4">
-        <v>-0.6906623513955199</v>
+        <v>-0.8328389495333018</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alpha Services and Holdings S.A. (ATSE:ALPHA)</t>
+          <t>Eurobank Ergasias Services and Holdings S.A. (ATSE:EUROB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,13 +954,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.157</v>
+        <v>0.195</v>
       </c>
       <c r="E5">
-        <v>0.46</v>
+        <v>0.65</v>
       </c>
       <c r="F5">
-        <v>0.0364</v>
+        <v>0.0218</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,85 +975,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>672.1</v>
+        <v>1444.3</v>
       </c>
       <c r="L5">
-        <v>0.3441196047309406</v>
+        <v>0.456133148054573</v>
       </c>
       <c r="M5">
-        <v>110.3</v>
+        <v>491.8</v>
       </c>
       <c r="N5">
-        <v>0.02836642320748894</v>
+        <v>0.05797272287906829</v>
       </c>
       <c r="O5">
-        <v>0.1641124832614194</v>
+        <v>0.3405109741743405</v>
       </c>
       <c r="P5">
-        <v>68.90000000000001</v>
+        <v>381.4</v>
       </c>
       <c r="Q5">
-        <v>0.01771937043514042</v>
+        <v>0.04495891928848444</v>
       </c>
       <c r="R5">
-        <v>0.1025145067698259</v>
+        <v>0.2640725611022641</v>
       </c>
       <c r="S5">
-        <v>41.40000000000001</v>
+        <v>110.4</v>
       </c>
       <c r="T5">
-        <v>0.3753399818676337</v>
+        <v>0.2244814965433103</v>
       </c>
       <c r="U5">
-        <v>4953.9</v>
+        <v>19417.8</v>
       </c>
       <c r="V5">
-        <v>1.274020162534719</v>
+        <v>2.288944160880789</v>
       </c>
       <c r="W5">
-        <v>0.08895153392096138</v>
+        <v>0.1805239607029473</v>
       </c>
       <c r="X5">
-        <v>0.1263983231757652</v>
+        <v>0.1179543777023059</v>
       </c>
       <c r="Y5">
-        <v>-0.03744678925480378</v>
+        <v>0.06256958300064133</v>
       </c>
       <c r="Z5">
-        <v>0.2585312260079951</v>
+        <v>0.1647639167854801</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.08958989407022958</v>
+        <v>0.08876853438037652</v>
       </c>
       <c r="AC5">
-        <v>-0.08958989407022958</v>
+        <v>-0.08876853438037652</v>
       </c>
       <c r="AD5">
-        <v>8316.200000000001</v>
+        <v>15107.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>8316.200000000001</v>
+        <v>15107.1</v>
       </c>
       <c r="AG5">
-        <v>3362.300000000001</v>
+        <v>-4310.699999999999</v>
       </c>
       <c r="AH5">
-        <v>0.6813988168395524</v>
+        <v>0.6403918543136191</v>
       </c>
       <c r="AI5">
-        <v>0.4829160085478026</v>
+        <v>0.5887595872045894</v>
       </c>
       <c r="AJ5">
-        <v>0.463720744204008</v>
+        <v>-1.033096870057038</v>
       </c>
       <c r="AK5">
-        <v>0.2740953297084023</v>
+        <v>-0.6906623513955199</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1079,120 +1070,343 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Alpha Services and Holdings S.A. (ATSE:ALPHA)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.157</v>
+      </c>
+      <c r="E6">
+        <v>0.46</v>
+      </c>
+      <c r="F6">
+        <v>0.0364</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>672.1</v>
+      </c>
+      <c r="L6">
+        <v>0.3441196047309406</v>
+      </c>
+      <c r="M6">
+        <v>110.3</v>
+      </c>
+      <c r="N6">
+        <v>0.02836642320748894</v>
+      </c>
+      <c r="O6">
+        <v>0.1641124832614194</v>
+      </c>
+      <c r="P6">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="Q6">
+        <v>0.01771937043514042</v>
+      </c>
+      <c r="R6">
+        <v>0.1025145067698259</v>
+      </c>
+      <c r="S6">
+        <v>41.40000000000001</v>
+      </c>
+      <c r="T6">
+        <v>0.3753399818676337</v>
+      </c>
+      <c r="U6">
+        <v>4953.9</v>
+      </c>
+      <c r="V6">
+        <v>1.274020162534719</v>
+      </c>
+      <c r="W6">
+        <v>0.08895153392096138</v>
+      </c>
+      <c r="X6">
+        <v>0.1263861100883135</v>
+      </c>
+      <c r="Y6">
+        <v>-0.03743457616735209</v>
+      </c>
+      <c r="Z6">
+        <v>0.2585312260079951</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.08958600296611743</v>
+      </c>
+      <c r="AC6">
+        <v>-0.08958600296611743</v>
+      </c>
+      <c r="AD6">
+        <v>8316.200000000001</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>8316.200000000001</v>
+      </c>
+      <c r="AG6">
+        <v>3362.300000000001</v>
+      </c>
+      <c r="AH6">
+        <v>0.6813988168395524</v>
+      </c>
+      <c r="AI6">
+        <v>0.4829160085478026</v>
+      </c>
+      <c r="AJ6">
+        <v>0.463720744204008</v>
+      </c>
+      <c r="AK6">
+        <v>0.2740953297084023</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Attica Bank S.A. (ATSE:TATT)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="K7">
+        <v>-369</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>319.5</v>
+      </c>
+      <c r="V7">
+        <v>0.2764319086347119</v>
+      </c>
+      <c r="W7">
+        <v>-0.8154696132596685</v>
+      </c>
+      <c r="X7">
+        <v>0.08299761335438989</v>
+      </c>
+      <c r="Y7">
+        <v>-0.8984672266140584</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.08960284844310795</v>
+      </c>
+      <c r="AC7">
+        <v>-0.08960284844310795</v>
+      </c>
+      <c r="AD7">
+        <v>343.2</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>343.2</v>
+      </c>
+      <c r="AG7">
+        <v>23.69999999999999</v>
+      </c>
+      <c r="AH7">
+        <v>0.22895263509006</v>
+      </c>
+      <c r="AI7">
+        <v>0.7234401349072512</v>
+      </c>
+      <c r="AJ7">
+        <v>0.02009325985587112</v>
+      </c>
+      <c r="AK7">
+        <v>0.1530019367333763</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Piraeus Financial Holdings S.A. (ATSE:TPEIR)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D6">
+      <c r="D8">
         <v>0.181</v>
       </c>
-      <c r="E6">
+      <c r="E8">
         <v>0.367</v>
       </c>
-      <c r="F6">
+      <c r="F8">
         <v>0.0369</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>1221.3</v>
       </c>
-      <c r="L6">
+      <c r="L8">
         <v>0.4018359490672194</v>
       </c>
-      <c r="M6">
+      <c r="M8">
         <v>213.262</v>
       </c>
-      <c r="N6">
+      <c r="N8">
         <v>0.04291935840930589</v>
       </c>
-      <c r="O6">
+      <c r="O8">
         <v>0.1746188487677066</v>
       </c>
-      <c r="P6">
+      <c r="P8">
         <v>87.262</v>
       </c>
-      <c r="Q6">
+      <c r="Q8">
         <v>0.01756163335949607</v>
       </c>
-      <c r="R6">
+      <c r="R8">
         <v>0.07145009416195858</v>
       </c>
-      <c r="S6">
+      <c r="S8">
         <v>126</v>
       </c>
-      <c r="T6">
+      <c r="T8">
         <v>0.5908225562922602</v>
       </c>
-      <c r="U6">
+      <c r="U8">
         <v>11377.4</v>
       </c>
-      <c r="V6">
+      <c r="V8">
         <v>2.289722071283383</v>
       </c>
-      <c r="W6">
+      <c r="W8">
         <v>0.1624501197126896</v>
       </c>
-      <c r="X6">
-        <v>0.1188186433747245</v>
-      </c>
-      <c r="Y6">
-        <v>0.04363147633796502</v>
-      </c>
-      <c r="Z6">
+      <c r="X8">
+        <v>0.118807578838367</v>
+      </c>
+      <c r="Y8">
+        <v>0.04364254087432259</v>
+      </c>
+      <c r="Z8">
         <v>0.4645755949924337</v>
       </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.09082676373974205</v>
-      </c>
-      <c r="AC6">
-        <v>-0.09082676373974205</v>
-      </c>
-      <c r="AD6">
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.09082283599730895</v>
+      </c>
+      <c r="AC8">
+        <v>-0.09082283599730895</v>
+      </c>
+      <c r="AD8">
         <v>9028.6</v>
       </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
         <v>9028.6</v>
       </c>
-      <c r="AG6">
+      <c r="AG8">
         <v>-2348.799999999999</v>
       </c>
-      <c r="AH6">
+      <c r="AH8">
         <v>0.6450151812823719</v>
       </c>
-      <c r="AI6">
+      <c r="AI8">
         <v>0.498308358859729</v>
       </c>
-      <c r="AJ6">
+      <c r="AJ8">
         <v>-0.8964543338040529</v>
       </c>
-      <c r="AK6">
+      <c r="AK8">
         <v>-0.3484297814896677</v>
       </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
         <v>0</v>
       </c>
     </row>
